--- a/ig/DM-OCTOBRE-2026/ValueSet-jdv-localisation-hemorragie-cerebrale-cisis.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-jdv-localisation-hemorragie-cerebrale-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260916095453</t>
+    <t>20260928134049</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T09:54:53+01:00</t>
+    <t>2026-09-28T13:40:49+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -136,7 +136,7 @@
     <t>15926001</t>
   </si>
   <si>
-    <t>tronc de l'encéphale</t>
+    <t>tronc cérébral</t>
   </si>
   <si>
     <t>35764002</t>
